--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -6098,10 +6098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131651200</v>
+        <v>131651222</v>
       </c>
       <c r="B44" t="n">
-        <v>80365</v>
+        <v>91824</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6109,26 +6109,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R44" t="n">
-        <v>7017008</v>
+        <v>7016908</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6191,27 +6195,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6229,10 +6233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131651222</v>
+        <v>131651200</v>
       </c>
       <c r="B45" t="n">
-        <v>91824</v>
+        <v>80365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6240,30 +6244,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R45" t="n">
-        <v>7016908</v>
+        <v>7017008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651232</v>
+        <v>131651197</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493294</v>
+        <v>493219</v>
       </c>
       <c r="R2" t="n">
-        <v>7016924</v>
+        <v>7017136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,14 +781,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651174</v>
+        <v>131651232</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,31 +822,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493215</v>
+        <v>493294</v>
       </c>
       <c r="R3" t="n">
-        <v>7016987</v>
+        <v>7016924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -918,12 +919,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651197</v>
+        <v>131651174</v>
       </c>
       <c r="B4" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +953,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493219</v>
+        <v>493215</v>
       </c>
       <c r="R4" t="n">
-        <v>7017136</v>
+        <v>7016987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,13 +1034,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,19 +1052,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651206</v>
+        <v>131651208</v>
       </c>
       <c r="B5" t="n">
         <v>80401</v>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493377</v>
+        <v>493289</v>
       </c>
       <c r="R5" t="n">
-        <v>7017100</v>
+        <v>7016944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651177</v>
+        <v>131651206</v>
       </c>
       <c r="B6" t="n">
-        <v>80394</v>
+        <v>80401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493347</v>
+        <v>493377</v>
       </c>
       <c r="R6" t="n">
-        <v>7017111</v>
+        <v>7017100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651208</v>
+        <v>131651177</v>
       </c>
       <c r="B7" t="n">
-        <v>80401</v>
+        <v>80394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493289</v>
+        <v>493347</v>
       </c>
       <c r="R7" t="n">
-        <v>7016944</v>
+        <v>7017111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131651195</v>
+        <v>131651230</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,30 +1983,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2014,10 +2010,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493285</v>
+        <v>493317</v>
       </c>
       <c r="R12" t="n">
-        <v>7017159</v>
+        <v>7017104</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2069,22 +2065,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2102,10 +2098,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131651230</v>
+        <v>131651195</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2113,26 +2109,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493317</v>
+        <v>493285</v>
       </c>
       <c r="R13" t="n">
-        <v>7017104</v>
+        <v>7017159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2195,22 +2195,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,28 +2499,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2530,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R16" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2571,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2580,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651170</v>
+        <v>131651198</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2764,29 +2764,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2796,10 +2795,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R18" t="n">
-        <v>7017120</v>
+        <v>7017133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2836,7 +2835,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2845,6 +2844,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3149,39 +3149,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131651178</v>
+        <v>131651172</v>
       </c>
       <c r="B21" t="n">
-        <v>80394</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493301</v>
+        <v>493291</v>
       </c>
       <c r="R21" t="n">
-        <v>7017157</v>
+        <v>7017105</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3229,13 +3230,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3246,22 +3251,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3279,40 +3284,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131651172</v>
+        <v>131651178</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3322,10 +3326,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493291</v>
+        <v>493301</v>
       </c>
       <c r="R22" t="n">
-        <v>7017105</v>
+        <v>7017157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3360,17 +3364,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3414,37 +3414,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>80401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R23" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3490,11 +3494,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3512,22 +3511,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,10 +3544,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651168</v>
+        <v>131651231</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3556,31 +3555,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3588,10 +3582,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493227</v>
+        <v>493312</v>
       </c>
       <c r="R24" t="n">
-        <v>7017123</v>
+        <v>7016962</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3628,7 +3622,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3637,6 +3631,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3657,12 +3652,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3680,39 +3675,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651203</v>
+        <v>131651168</v>
       </c>
       <c r="B25" t="n">
-        <v>80401</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3722,10 +3718,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493344</v>
+        <v>493227</v>
       </c>
       <c r="R25" t="n">
-        <v>7017110</v>
+        <v>7017123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3760,13 +3756,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3777,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4071,38 +4071,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651192</v>
+        <v>131651165</v>
       </c>
       <c r="B28" t="n">
-        <v>97898</v>
+        <v>91828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4110,10 +4113,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493258</v>
+        <v>493266</v>
       </c>
       <c r="R28" t="n">
-        <v>7016969</v>
+        <v>7016915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4161,6 +4164,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4178,10 +4201,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131651165</v>
+        <v>131651224</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>91848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4189,23 +4212,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -4220,10 +4239,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493266</v>
+        <v>493343</v>
       </c>
       <c r="R29" t="n">
-        <v>7016915</v>
+        <v>7017125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4258,6 +4277,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4285,12 +4309,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4434,37 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651224</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>91848</v>
+        <v>97898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4472,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493343</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7017125</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4510,11 +4535,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4695,41 +4695,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651183</v>
+        <v>131651199</v>
       </c>
       <c r="B33" t="n">
-        <v>80394</v>
+        <v>80365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4737,10 +4733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493286</v>
+        <v>493372</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7017082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4777,7 +4773,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en klenvuxen sälg.</t>
+          <t>Enstaka bålar på en klen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4830,39 +4826,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131651196</v>
+        <v>131651179</v>
       </c>
       <c r="B34" t="n">
-        <v>80365</v>
+        <v>80394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4872,10 +4868,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493219</v>
+        <v>493247</v>
       </c>
       <c r="R34" t="n">
-        <v>7017124</v>
+        <v>7017116</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4908,11 +4904,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4965,7 +4956,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131651199</v>
+        <v>131651196</v>
       </c>
       <c r="B35" t="n">
         <v>80365</v>
@@ -4995,7 +4986,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5003,10 +4998,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493372</v>
+        <v>493219</v>
       </c>
       <c r="R35" t="n">
-        <v>7017082</v>
+        <v>7017124</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5043,7 +5038,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen sälg.</t>
+          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5096,7 +5091,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131651179</v>
+        <v>131651183</v>
       </c>
       <c r="B36" t="n">
         <v>80394</v>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493247</v>
+        <v>493286</v>
       </c>
       <c r="R36" t="n">
-        <v>7017116</v>
+        <v>7016955</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5174,6 +5169,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131651169</v>
+        <v>131651225</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,29 +5237,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493230</v>
+        <v>493294</v>
       </c>
       <c r="R37" t="n">
-        <v>7017123</v>
+        <v>7017032</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5309,7 +5304,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5318,6 +5313,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5343,7 +5339,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5361,10 +5357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131651225</v>
+        <v>131651169</v>
       </c>
       <c r="B38" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5372,24 +5368,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5399,10 +5400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493294</v>
+        <v>493230</v>
       </c>
       <c r="R38" t="n">
-        <v>7017032</v>
+        <v>7017123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5439,7 +5440,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5448,7 +5449,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5706,39 +5706,35 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B41" t="n">
-        <v>80394</v>
+        <v>91848</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,37 +5837,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>91848</v>
+        <v>80269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5914,7 +5915,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5934,22 +5935,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,10 +5968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B43" t="n">
-        <v>80269</v>
+        <v>80394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5978,26 +5979,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R43" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6043,11 +6048,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651189</v>
+        <v>131651229</v>
       </c>
       <c r="B46" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,54 +6375,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493301</v>
+        <v>493259</v>
       </c>
       <c r="R46" t="n">
-        <v>7016941</v>
+        <v>7017152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6457,23 +6440,39 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6491,10 +6490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651202</v>
+        <v>131651228</v>
       </c>
       <c r="B47" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6502,21 +6501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6529,10 +6528,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493288</v>
+        <v>493283</v>
       </c>
       <c r="R47" t="n">
-        <v>7016954</v>
+        <v>7017147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6569,7 +6568,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6589,22 +6588,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6622,10 +6621,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651173</v>
+        <v>131651202</v>
       </c>
       <c r="B48" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6633,31 +6632,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6665,10 +6659,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493227</v>
+        <v>493288</v>
       </c>
       <c r="R48" t="n">
-        <v>7017003</v>
+        <v>7016954</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6705,7 +6699,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6714,6 +6708,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6724,22 +6719,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6757,10 +6752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651228</v>
+        <v>131651189</v>
       </c>
       <c r="B49" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6768,37 +6763,54 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493283</v>
+        <v>493301</v>
       </c>
       <c r="R49" t="n">
-        <v>7017147</v>
+        <v>7016941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6835,7 +6847,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6844,33 +6856,12 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6888,10 +6879,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651229</v>
+        <v>131651173</v>
       </c>
       <c r="B50" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6899,26 +6890,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493259</v>
+        <v>493227</v>
       </c>
       <c r="R50" t="n">
-        <v>7017152</v>
+        <v>7017003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6964,13 +6960,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7014,40 +7014,39 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131651167</v>
+        <v>131651185</v>
       </c>
       <c r="B51" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7057,10 +7056,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493229</v>
+        <v>493234</v>
       </c>
       <c r="R51" t="n">
-        <v>7017129</v>
+        <v>7016744</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7095,17 +7094,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död delvis avbarkad gran med äldre sannolika födosökspår av tretåig hackspett. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7116,22 +7111,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7149,39 +7144,40 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131651185</v>
+        <v>131651167</v>
       </c>
       <c r="B52" t="n">
-        <v>80394</v>
+        <v>57898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7191,10 +7187,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493234</v>
+        <v>493229</v>
       </c>
       <c r="R52" t="n">
-        <v>7016744</v>
+        <v>7017129</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7229,13 +7225,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död delvis avbarkad gran med äldre sannolika födosökspår av tretåig hackspett. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7246,22 +7246,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7279,37 +7279,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131651227</v>
+        <v>131651186</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>80394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7317,10 +7321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493333</v>
+        <v>493229</v>
       </c>
       <c r="R53" t="n">
-        <v>7017135</v>
+        <v>7016761</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7355,11 +7359,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långväxta bålar blandade med andra hänglavar på en gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7377,22 +7376,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7410,41 +7409,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131651186</v>
+        <v>131651227</v>
       </c>
       <c r="B54" t="n">
-        <v>80394</v>
+        <v>79260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7452,10 +7447,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493229</v>
+        <v>493333</v>
       </c>
       <c r="R54" t="n">
-        <v>7016761</v>
+        <v>7017135</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7490,6 +7485,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar blandade med andra hänglavar på en gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7507,22 +7507,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -2488,40 +2488,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>80401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2531,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R16" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2569,17 +2568,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2585,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2618,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B17" t="n">
-        <v>80401</v>
+        <v>80365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R17" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,6 +2696,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2764,28 +2764,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2795,10 +2796,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R18" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2835,7 +2836,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2844,7 +2845,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3149,40 +3149,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131651172</v>
+        <v>131651178</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493291</v>
+        <v>493301</v>
       </c>
       <c r="R21" t="n">
-        <v>7017105</v>
+        <v>7017157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3230,17 +3229,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3251,22 +3246,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3284,39 +3279,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131651178</v>
+        <v>131651172</v>
       </c>
       <c r="B22" t="n">
-        <v>80394</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3326,10 +3322,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493301</v>
+        <v>493291</v>
       </c>
       <c r="R22" t="n">
-        <v>7017157</v>
+        <v>7017105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3364,13 +3360,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651197</v>
+        <v>131651232</v>
       </c>
       <c r="B2" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493219</v>
+        <v>493294</v>
       </c>
       <c r="R2" t="n">
-        <v>7017136</v>
+        <v>7016924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,19 +781,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651232</v>
+        <v>131651197</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493294</v>
+        <v>493219</v>
       </c>
       <c r="R3" t="n">
-        <v>7016924</v>
+        <v>7017136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,14 +912,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651208</v>
+        <v>131651191</v>
       </c>
       <c r="B5" t="n">
-        <v>80401</v>
+        <v>97899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,30 +1088,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493289</v>
+        <v>493254</v>
       </c>
       <c r="R5" t="n">
-        <v>7016944</v>
+        <v>7017114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,24 +1169,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1467,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651191</v>
+        <v>131651208</v>
       </c>
       <c r="B8" t="n">
-        <v>97898</v>
+        <v>80401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1460,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1506,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493254</v>
+        <v>493289</v>
       </c>
       <c r="R8" t="n">
-        <v>7017114</v>
+        <v>7016944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,9 +1544,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131651230</v>
+        <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,26 +1983,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2010,10 +2014,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493317</v>
+        <v>493285</v>
       </c>
       <c r="R12" t="n">
-        <v>7017104</v>
+        <v>7017159</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2065,22 +2069,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,10 +2102,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131651195</v>
+        <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,30 +2113,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493285</v>
+        <v>493317</v>
       </c>
       <c r="R13" t="n">
-        <v>7017159</v>
+        <v>7017104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2195,22 +2195,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2488,32 +2488,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>80401</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R16" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2566,6 +2566,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2618,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651198</v>
+        <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>80401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493220</v>
+        <v>493230</v>
       </c>
       <c r="R17" t="n">
-        <v>7017133</v>
+        <v>7016768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2696,11 +2701,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2888,37 +2888,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B19" t="n">
-        <v>80401</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2926,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R19" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,13 +2969,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2981,22 +2990,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3014,42 +3023,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>80401</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R20" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,17 +3099,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3414,39 +3414,40 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651203</v>
+        <v>131651168</v>
       </c>
       <c r="B23" t="n">
-        <v>80401</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3456,10 +3457,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493344</v>
+        <v>493227</v>
       </c>
       <c r="R23" t="n">
-        <v>7017110</v>
+        <v>7017123</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3494,13 +3495,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3511,22 +3516,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3675,40 +3680,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651168</v>
+        <v>131651203</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>80401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3718,10 +3722,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493227</v>
+        <v>493344</v>
       </c>
       <c r="R25" t="n">
-        <v>7017123</v>
+        <v>7017110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3756,17 +3760,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3777,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4071,41 +4071,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651165</v>
+        <v>131651192</v>
       </c>
       <c r="B28" t="n">
-        <v>91828</v>
+        <v>97899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4113,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493266</v>
+        <v>493258</v>
       </c>
       <c r="R28" t="n">
-        <v>7016915</v>
+        <v>7016969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4164,26 +4161,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4201,10 +4178,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131651224</v>
+        <v>131651226</v>
       </c>
       <c r="B29" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4212,26 +4189,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4239,10 +4216,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493343</v>
+        <v>493370</v>
       </c>
       <c r="R29" t="n">
-        <v>7017125</v>
+        <v>7017120</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4277,11 +4254,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4309,12 +4281,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4332,10 +4304,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651226</v>
+        <v>131651224</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4343,26 +4315,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4370,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493370</v>
+        <v>493343</v>
       </c>
       <c r="R30" t="n">
-        <v>7017120</v>
+        <v>7017125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4408,6 +4380,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4435,12 +4412,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,38 +4435,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651192</v>
+        <v>131651165</v>
       </c>
       <c r="B31" t="n">
-        <v>97898</v>
+        <v>91828</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4497,10 +4477,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493258</v>
+        <v>493266</v>
       </c>
       <c r="R31" t="n">
-        <v>7016969</v>
+        <v>7016915</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4548,6 +4528,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4695,37 +4695,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651199</v>
+        <v>131651183</v>
       </c>
       <c r="B33" t="n">
-        <v>80365</v>
+        <v>80394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4733,10 +4737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493372</v>
+        <v>493286</v>
       </c>
       <c r="R33" t="n">
-        <v>7017082</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4773,7 +4777,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen sälg.</t>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4826,39 +4830,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131651179</v>
+        <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80394</v>
+        <v>80365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4868,10 +4872,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493247</v>
+        <v>493219</v>
       </c>
       <c r="R34" t="n">
-        <v>7017116</v>
+        <v>7017124</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4904,6 +4908,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4956,7 +4965,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131651196</v>
+        <v>131651199</v>
       </c>
       <c r="B35" t="n">
         <v>80365</v>
@@ -4986,11 +4995,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4998,10 +5003,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493219</v>
+        <v>493372</v>
       </c>
       <c r="R35" t="n">
-        <v>7017124</v>
+        <v>7017082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5038,7 +5043,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
+          <t>Enstaka bålar på en klen sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5091,7 +5096,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131651183</v>
+        <v>131651179</v>
       </c>
       <c r="B36" t="n">
         <v>80394</v>
@@ -5133,10 +5138,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493286</v>
+        <v>493247</v>
       </c>
       <c r="R36" t="n">
-        <v>7016955</v>
+        <v>7017116</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5169,11 +5174,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5495,7 +5495,7 @@
         <v>131651193</v>
       </c>
       <c r="B39" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>131651194</v>
       </c>
       <c r="B40" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5706,35 +5706,39 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>91848</v>
+        <v>80394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,22 +5803,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5968,39 +5967,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80394</v>
+        <v>91848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,6 +6043,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131651222</v>
+        <v>131651200</v>
       </c>
       <c r="B44" t="n">
-        <v>91824</v>
+        <v>80365</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6109,30 +6109,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6140,10 +6136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R44" t="n">
-        <v>7016908</v>
+        <v>7017008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6180,7 +6176,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6195,27 +6191,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6233,10 +6229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131651200</v>
+        <v>131651222</v>
       </c>
       <c r="B45" t="n">
-        <v>80365</v>
+        <v>91824</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6244,26 +6240,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R45" t="n">
-        <v>7017008</v>
+        <v>7016908</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651229</v>
+        <v>131651173</v>
       </c>
       <c r="B46" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,26 +6375,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6402,10 +6407,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493259</v>
+        <v>493227</v>
       </c>
       <c r="R46" t="n">
-        <v>7017152</v>
+        <v>7017003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6440,13 +6445,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6467,12 +6476,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6490,10 +6499,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651228</v>
+        <v>131651189</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6501,37 +6510,54 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493283</v>
+        <v>493301</v>
       </c>
       <c r="R47" t="n">
-        <v>7017147</v>
+        <v>7016941</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6568,7 +6594,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6577,33 +6603,12 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6752,10 +6757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651189</v>
+        <v>131651228</v>
       </c>
       <c r="B49" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6763,54 +6768,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493301</v>
+        <v>493283</v>
       </c>
       <c r="R49" t="n">
-        <v>7016941</v>
+        <v>7017147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6847,7 +6835,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6856,12 +6844,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6879,10 +6888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651173</v>
+        <v>131651229</v>
       </c>
       <c r="B50" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6890,31 +6899,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6922,10 +6926,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493227</v>
+        <v>493259</v>
       </c>
       <c r="R50" t="n">
-        <v>7017003</v>
+        <v>7017152</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6960,17 +6964,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7279,41 +7279,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131651186</v>
+        <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>80394</v>
+        <v>79260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7321,10 +7317,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493229</v>
+        <v>493333</v>
       </c>
       <c r="R53" t="n">
-        <v>7016761</v>
+        <v>7017135</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7359,6 +7355,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långväxta bålar blandade med andra hänglavar på en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7376,22 +7377,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7409,37 +7410,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131651227</v>
+        <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>80394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7447,10 +7452,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493333</v>
+        <v>493229</v>
       </c>
       <c r="R54" t="n">
-        <v>7017135</v>
+        <v>7016761</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7485,11 +7490,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar blandade med andra hänglavar på en gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7507,22 +7507,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131651232</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131651197</v>
       </c>
       <c r="B3" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>131651174</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651191</v>
+        <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>97899</v>
+        <v>80402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,27 +1088,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1116,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493254</v>
+        <v>493377</v>
       </c>
       <c r="R5" t="n">
-        <v>7017114</v>
+        <v>7017100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1169,9 +1172,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651206</v>
+        <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80401</v>
+        <v>80395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1231,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493377</v>
+        <v>493347</v>
       </c>
       <c r="R6" t="n">
-        <v>7017100</v>
+        <v>7017111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1319,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651177</v>
+        <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80394</v>
+        <v>80402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1361,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493347</v>
+        <v>493289</v>
       </c>
       <c r="R7" t="n">
-        <v>7017111</v>
+        <v>7016944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1449,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651208</v>
+        <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>80401</v>
+        <v>97900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,30 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1491,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493289</v>
+        <v>493254</v>
       </c>
       <c r="R8" t="n">
-        <v>7016944</v>
+        <v>7017114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,24 +1559,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
         <v>131651204</v>
       </c>
       <c r="B9" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>131651176</v>
       </c>
       <c r="B11" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,42 +2888,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>80402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2931,10 +2926,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R19" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,17 +2964,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2990,22 +2981,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3023,37 +3014,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>80401</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3061,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R20" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3099,13 +3095,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3149,39 +3149,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131651178</v>
+        <v>131651172</v>
       </c>
       <c r="B21" t="n">
-        <v>80394</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493301</v>
+        <v>493291</v>
       </c>
       <c r="R21" t="n">
-        <v>7017157</v>
+        <v>7017105</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3229,13 +3230,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3246,22 +3251,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3279,40 +3284,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131651172</v>
+        <v>131651178</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>80395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3322,10 +3326,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493291</v>
+        <v>493301</v>
       </c>
       <c r="R22" t="n">
-        <v>7017105</v>
+        <v>7017157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3360,17 +3364,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
         <v>131651168</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>131651231</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>131651203</v>
       </c>
       <c r="B25" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4071,38 +4071,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651192</v>
+        <v>131651165</v>
       </c>
       <c r="B28" t="n">
-        <v>97899</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4110,10 +4113,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493258</v>
+        <v>493266</v>
       </c>
       <c r="R28" t="n">
-        <v>7016969</v>
+        <v>7016915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4161,6 +4164,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4181,7 +4204,7 @@
         <v>131651226</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4307,7 +4330,7 @@
         <v>131651224</v>
       </c>
       <c r="B30" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4435,41 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651165</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>91828</v>
+        <v>97900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4477,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493266</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7016915</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
         <v>131651184</v>
       </c>
       <c r="B32" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>131651183</v>
       </c>
       <c r="B33" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131651199</v>
       </c>
       <c r="B35" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131651179</v>
       </c>
       <c r="B36" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131651225</v>
       </c>
       <c r="B37" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>131651169</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B39" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R39" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B40" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R40" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5706,39 +5706,35 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B41" t="n">
-        <v>80394</v>
+        <v>91849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,10 +5837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B42" t="n">
-        <v>80269</v>
+        <v>80395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5847,26 +5848,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5912,11 +5917,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>80270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
         <v>131651200</v>
       </c>
       <c r="B44" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>131651222</v>
       </c>
       <c r="B45" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651173</v>
+        <v>131651189</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>57896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,16 +6375,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6392,25 +6392,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493227</v>
+        <v>493301</v>
       </c>
       <c r="R46" t="n">
-        <v>7017003</v>
+        <v>7016941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6447,7 +6459,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6462,26 +6474,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6499,10 +6491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651189</v>
+        <v>131651202</v>
       </c>
       <c r="B47" t="n">
-        <v>57895</v>
+        <v>80366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6510,54 +6502,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493301</v>
+        <v>493288</v>
       </c>
       <c r="R47" t="n">
-        <v>7016941</v>
+        <v>7016954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6594,7 +6569,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6603,12 +6578,33 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6626,10 +6622,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651202</v>
+        <v>131651228</v>
       </c>
       <c r="B48" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6637,21 +6633,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6664,10 +6660,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493288</v>
+        <v>493283</v>
       </c>
       <c r="R48" t="n">
-        <v>7016954</v>
+        <v>7017147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6704,7 +6700,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6724,22 +6720,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6757,10 +6753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651228</v>
+        <v>131651229</v>
       </c>
       <c r="B49" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6795,10 +6791,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493283</v>
+        <v>493259</v>
       </c>
       <c r="R49" t="n">
-        <v>7017147</v>
+        <v>7017152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6831,11 +6827,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6888,10 +6879,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651229</v>
+        <v>131651173</v>
       </c>
       <c r="B50" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6899,26 +6890,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493259</v>
+        <v>493227</v>
       </c>
       <c r="R50" t="n">
-        <v>7017152</v>
+        <v>7017003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6964,13 +6960,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
         <v>131651185</v>
       </c>
       <c r="B51" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>131651167</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651232</v>
+        <v>131651174</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493294</v>
+        <v>493215</v>
       </c>
       <c r="R2" t="n">
-        <v>7016924</v>
+        <v>7016987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,13 +767,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -783,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651197</v>
+        <v>131651232</v>
       </c>
       <c r="B3" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493219</v>
+        <v>493294</v>
       </c>
       <c r="R3" t="n">
-        <v>7017136</v>
+        <v>7016924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,19 +916,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,31 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R4" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,12 +1028,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1052,14 +1047,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
         <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,52 +1579,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651204</v>
+        <v>131651176</v>
       </c>
       <c r="B9" t="n">
-        <v>80402</v>
+        <v>58061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493221</v>
+        <v>493288</v>
       </c>
       <c r="R9" t="n">
-        <v>7017135</v>
+        <v>7016960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,13 +1668,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1674,24 +1687,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651181</v>
+        <v>131651204</v>
       </c>
       <c r="B10" t="n">
-        <v>80395</v>
+        <v>80405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,21 +1718,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1751,10 +1749,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493364</v>
+        <v>493221</v>
       </c>
       <c r="R10" t="n">
-        <v>7017079</v>
+        <v>7017135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,11 +1787,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en klen rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1811,12 +1804,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1826,7 +1819,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,61 +1837,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B11" t="n">
-        <v>58058</v>
+        <v>80398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R11" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1919,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,6 +1928,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1952,9 +1937,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B16" t="n">
-        <v>80366</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,28 +2499,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2530,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R16" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2571,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2580,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B17" t="n">
-        <v>80402</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R17" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,40 +2758,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>80405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R18" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,17 +2838,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
         <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3149,40 +3149,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131651172</v>
+        <v>131651178</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>80398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493291</v>
+        <v>493301</v>
       </c>
       <c r="R21" t="n">
-        <v>7017105</v>
+        <v>7017157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3230,17 +3229,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3251,22 +3246,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3284,39 +3279,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131651178</v>
+        <v>131651172</v>
       </c>
       <c r="B22" t="n">
-        <v>80395</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3326,10 +3322,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493301</v>
+        <v>493291</v>
       </c>
       <c r="R22" t="n">
-        <v>7017157</v>
+        <v>7017105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3364,13 +3360,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651168</v>
+        <v>131651231</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3425,31 +3425,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3457,10 +3452,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493227</v>
+        <v>493312</v>
       </c>
       <c r="R23" t="n">
-        <v>7017123</v>
+        <v>7016962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3497,7 +3492,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3506,6 +3501,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3526,12 +3522,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3549,37 +3545,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>80405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R24" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,11 +3625,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3647,22 +3642,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3680,39 +3675,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651203</v>
+        <v>131651168</v>
       </c>
       <c r="B25" t="n">
-        <v>80402</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3722,10 +3718,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493344</v>
+        <v>493227</v>
       </c>
       <c r="R25" t="n">
-        <v>7017110</v>
+        <v>7017123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3760,13 +3756,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3777,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>131651165</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>131651226</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4327,37 +4327,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651224</v>
+        <v>131651192</v>
       </c>
       <c r="B30" t="n">
-        <v>91849</v>
+        <v>97903</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4365,10 +4366,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493343</v>
+        <v>493258</v>
       </c>
       <c r="R30" t="n">
-        <v>7017125</v>
+        <v>7016969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4403,11 +4404,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4421,26 +4417,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,38 +4434,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651192</v>
+        <v>131651224</v>
       </c>
       <c r="B31" t="n">
-        <v>97900</v>
+        <v>91852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4497,10 +4472,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493258</v>
+        <v>493343</v>
       </c>
       <c r="R31" t="n">
-        <v>7016969</v>
+        <v>7017125</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,6 +4510,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4548,6 +4528,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
         <v>131651184</v>
       </c>
       <c r="B32" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>131651183</v>
       </c>
       <c r="B33" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131651199</v>
       </c>
       <c r="B35" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131651179</v>
       </c>
       <c r="B36" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131651225</v>
       </c>
       <c r="B37" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>131651169</v>
       </c>
       <c r="B38" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B39" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R39" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B40" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R40" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5706,35 +5706,39 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>91849</v>
+        <v>80398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,22 +5803,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,10 +5836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651187</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>80395</v>
+        <v>80273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5848,30 +5847,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5879,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493275</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7016819</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5917,6 +5912,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80270</v>
+        <v>91852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
         <v>131651200</v>
       </c>
       <c r="B44" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>131651222</v>
       </c>
       <c r="B45" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651189</v>
+        <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>80369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,54 +6375,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493301</v>
+        <v>493288</v>
       </c>
       <c r="R46" t="n">
-        <v>7016941</v>
+        <v>7016954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6459,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6468,12 +6451,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6491,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651202</v>
+        <v>131651228</v>
       </c>
       <c r="B47" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6502,21 +6506,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6529,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493288</v>
+        <v>493283</v>
       </c>
       <c r="R47" t="n">
-        <v>7016954</v>
+        <v>7017147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6569,7 +6573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6589,22 +6593,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6622,10 +6626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651228</v>
+        <v>131651229</v>
       </c>
       <c r="B48" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6660,10 +6664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493283</v>
+        <v>493259</v>
       </c>
       <c r="R48" t="n">
-        <v>7017147</v>
+        <v>7017152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6696,11 +6700,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6753,10 +6752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651229</v>
+        <v>131651189</v>
       </c>
       <c r="B49" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6764,37 +6763,54 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493259</v>
+        <v>493301</v>
       </c>
       <c r="R49" t="n">
-        <v>7017152</v>
+        <v>7016941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6829,39 +6845,23 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6882,7 +6882,7 @@
         <v>131651173</v>
       </c>
       <c r="B50" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>131651185</v>
       </c>
       <c r="B51" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>131651167</v>
       </c>
       <c r="B52" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R2" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,12 +762,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -785,14 +781,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651232</v>
+        <v>131651174</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,26 +822,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493294</v>
+        <v>493215</v>
       </c>
       <c r="R3" t="n">
-        <v>7016924</v>
+        <v>7016987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,13 +903,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -918,12 +923,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651197</v>
+        <v>131651232</v>
       </c>
       <c r="B4" t="n">
-        <v>80369</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +957,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493219</v>
+        <v>493294</v>
       </c>
       <c r="R4" t="n">
-        <v>7017136</v>
+        <v>7016924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,19 +1052,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651206</v>
+        <v>131651191</v>
       </c>
       <c r="B5" t="n">
-        <v>80405</v>
+        <v>97903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,30 +1088,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493377</v>
+        <v>493254</v>
       </c>
       <c r="R5" t="n">
-        <v>7017100</v>
+        <v>7017114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,24 +1169,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651177</v>
+        <v>131651206</v>
       </c>
       <c r="B6" t="n">
-        <v>80398</v>
+        <v>80405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1200,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493347</v>
+        <v>493377</v>
       </c>
       <c r="R6" t="n">
-        <v>7017111</v>
+        <v>7017100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651208</v>
+        <v>131651177</v>
       </c>
       <c r="B7" t="n">
-        <v>80405</v>
+        <v>80398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,21 +1330,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1379,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493289</v>
+        <v>493347</v>
       </c>
       <c r="R7" t="n">
-        <v>7016944</v>
+        <v>7017111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1467,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651191</v>
+        <v>131651208</v>
       </c>
       <c r="B8" t="n">
-        <v>97903</v>
+        <v>80405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1460,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1506,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493254</v>
+        <v>493289</v>
       </c>
       <c r="R8" t="n">
-        <v>7017114</v>
+        <v>7016944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,9 +1544,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,61 +1579,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651176</v>
+        <v>131651204</v>
       </c>
       <c r="B9" t="n">
-        <v>58061</v>
+        <v>80405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493288</v>
+        <v>493221</v>
       </c>
       <c r="R9" t="n">
-        <v>7016960</v>
+        <v>7017135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,17 +1659,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1687,9 +1674,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651204</v>
+        <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>80405</v>
+        <v>80398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,21 +1720,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1749,10 +1751,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493221</v>
+        <v>493364</v>
       </c>
       <c r="R10" t="n">
-        <v>7017135</v>
+        <v>7017079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1787,6 +1789,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1804,12 +1811,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1819,7 +1826,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1837,52 +1844,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B11" t="n">
-        <v>80398</v>
+        <v>58061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R11" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1935,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1928,7 +1944,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1937,24 +1952,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651170</v>
+        <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,29 +2499,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2531,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R16" t="n">
-        <v>7017120</v>
+        <v>7017133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2580,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651198</v>
+        <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>80405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493220</v>
+        <v>493230</v>
       </c>
       <c r="R17" t="n">
-        <v>7017133</v>
+        <v>7016768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2758,39 +2753,40 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651210</v>
+        <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>80405</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493230</v>
+        <v>493232</v>
       </c>
       <c r="R18" t="n">
-        <v>7016768</v>
+        <v>7017120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2838,13 +2834,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651165</v>
+        <v>131651226</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4082,30 +4082,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4113,10 +4109,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493266</v>
+        <v>493370</v>
       </c>
       <c r="R28" t="n">
-        <v>7016915</v>
+        <v>7017120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4178,12 +4174,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4201,10 +4197,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131651226</v>
+        <v>131651224</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4212,26 +4208,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4239,10 +4235,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493370</v>
+        <v>493343</v>
       </c>
       <c r="R29" t="n">
-        <v>7017120</v>
+        <v>7017125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4277,6 +4273,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4304,12 +4305,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,38 +4328,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651192</v>
+        <v>131651165</v>
       </c>
       <c r="B30" t="n">
-        <v>97903</v>
+        <v>91832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4366,10 +4370,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493258</v>
+        <v>493266</v>
       </c>
       <c r="R30" t="n">
-        <v>7016969</v>
+        <v>7016915</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4417,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4434,37 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651224</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>97903</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4472,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493343</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7017125</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4510,11 +4535,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5836,37 +5836,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B42" t="n">
-        <v>80273</v>
+        <v>91852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5934,22 +5934,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>80273</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651202</v>
+        <v>131651189</v>
       </c>
       <c r="B46" t="n">
-        <v>80369</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,37 +6375,54 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493288</v>
+        <v>493301</v>
       </c>
       <c r="R46" t="n">
-        <v>7016954</v>
+        <v>7016941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6442,7 +6459,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6451,33 +6468,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6495,10 +6491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651228</v>
+        <v>131651202</v>
       </c>
       <c r="B47" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6506,21 +6502,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6533,10 +6529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493283</v>
+        <v>493288</v>
       </c>
       <c r="R47" t="n">
-        <v>7017147</v>
+        <v>7016954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6573,7 +6569,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6593,22 +6589,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6626,7 +6622,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651229</v>
+        <v>131651228</v>
       </c>
       <c r="B48" t="n">
         <v>79264</v>
@@ -6664,10 +6660,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493259</v>
+        <v>493283</v>
       </c>
       <c r="R48" t="n">
-        <v>7017152</v>
+        <v>7017147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6700,6 +6696,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6752,10 +6753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651189</v>
+        <v>131651229</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6763,54 +6764,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493301</v>
+        <v>493259</v>
       </c>
       <c r="R49" t="n">
-        <v>7016941</v>
+        <v>7017152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6845,23 +6829,39 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651197</v>
+        <v>131651174</v>
       </c>
       <c r="B2" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493219</v>
+        <v>493215</v>
       </c>
       <c r="R2" t="n">
-        <v>7017136</v>
+        <v>7016987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,13 +767,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -781,19 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651174</v>
+        <v>131651232</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,31 +821,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493215</v>
+        <v>493294</v>
       </c>
       <c r="R3" t="n">
-        <v>7016987</v>
+        <v>7016924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,12 +897,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -923,12 +918,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651232</v>
+        <v>131651197</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493294</v>
+        <v>493219</v>
       </c>
       <c r="R4" t="n">
-        <v>7016924</v>
+        <v>7017136</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,14 +1047,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651191</v>
+        <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>97903</v>
+        <v>80405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,27 +1088,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1116,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493254</v>
+        <v>493377</v>
       </c>
       <c r="R5" t="n">
-        <v>7017114</v>
+        <v>7017100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1169,9 +1172,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651206</v>
+        <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80405</v>
+        <v>80398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1231,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493377</v>
+        <v>493347</v>
       </c>
       <c r="R6" t="n">
-        <v>7017100</v>
+        <v>7017111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1319,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651177</v>
+        <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80398</v>
+        <v>80405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1361,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493347</v>
+        <v>493289</v>
       </c>
       <c r="R7" t="n">
-        <v>7017111</v>
+        <v>7016944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1449,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651208</v>
+        <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>80405</v>
+        <v>97903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,30 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1491,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493289</v>
+        <v>493254</v>
       </c>
       <c r="R8" t="n">
-        <v>7016944</v>
+        <v>7017114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,24 +1559,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,28 +2499,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2530,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R16" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2571,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2580,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B17" t="n">
-        <v>80405</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R17" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,40 +2758,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>80405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R18" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,17 +2838,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651231</v>
+        <v>131651168</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3425,26 +3425,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3452,10 +3457,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493312</v>
+        <v>493227</v>
       </c>
       <c r="R23" t="n">
-        <v>7016962</v>
+        <v>7017123</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3492,7 +3497,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3501,7 +3506,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3522,12 +3526,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,41 +3549,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651203</v>
+        <v>131651231</v>
       </c>
       <c r="B24" t="n">
-        <v>80405</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493344</v>
+        <v>493312</v>
       </c>
       <c r="R24" t="n">
-        <v>7017110</v>
+        <v>7016962</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,6 +3625,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3642,22 +3647,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,40 +3680,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651168</v>
+        <v>131651203</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>80405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3718,10 +3722,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493227</v>
+        <v>493344</v>
       </c>
       <c r="R25" t="n">
-        <v>7017123</v>
+        <v>7017110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3756,17 +3760,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3777,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651226</v>
+        <v>131651224</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4082,26 +4082,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493370</v>
+        <v>493343</v>
       </c>
       <c r="R28" t="n">
-        <v>7017120</v>
+        <v>7017125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4147,6 +4147,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4174,12 +4179,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4197,10 +4202,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131651224</v>
+        <v>131651165</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4208,19 +4213,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -4235,10 +4244,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493343</v>
+        <v>493266</v>
       </c>
       <c r="R29" t="n">
-        <v>7017125</v>
+        <v>7016915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4273,11 +4282,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4305,12 +4309,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4328,41 +4332,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651165</v>
+        <v>131651192</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>97903</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4370,10 +4371,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493266</v>
+        <v>493258</v>
       </c>
       <c r="R30" t="n">
-        <v>7016915</v>
+        <v>7016969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4421,26 +4422,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,38 +4439,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651192</v>
+        <v>131651226</v>
       </c>
       <c r="B31" t="n">
-        <v>97903</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4497,10 +4477,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493258</v>
+        <v>493370</v>
       </c>
       <c r="R31" t="n">
-        <v>7016969</v>
+        <v>7017120</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4548,6 +4528,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B39" t="n">
         <v>97903</v>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R39" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B40" t="n">
         <v>97903</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R40" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5706,39 +5706,35 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B41" t="n">
-        <v>80398</v>
+        <v>91852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,35 +5837,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>80398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5874,10 +5879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R42" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5912,11 +5917,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,22 +5934,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131651200</v>
+        <v>131651222</v>
       </c>
       <c r="B44" t="n">
-        <v>80369</v>
+        <v>91828</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6109,26 +6109,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R44" t="n">
-        <v>7017008</v>
+        <v>7016908</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6191,27 +6195,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6229,10 +6233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131651222</v>
+        <v>131651200</v>
       </c>
       <c r="B45" t="n">
-        <v>91828</v>
+        <v>80369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6240,30 +6244,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R45" t="n">
-        <v>7016908</v>
+        <v>7017008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651189</v>
+        <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,54 +6375,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493301</v>
+        <v>493288</v>
       </c>
       <c r="R46" t="n">
-        <v>7016941</v>
+        <v>7016954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6459,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6468,12 +6451,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6491,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651202</v>
+        <v>131651228</v>
       </c>
       <c r="B47" t="n">
-        <v>80369</v>
+        <v>79264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6502,21 +6506,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6529,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493288</v>
+        <v>493283</v>
       </c>
       <c r="R47" t="n">
-        <v>7016954</v>
+        <v>7017147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6569,7 +6573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6589,22 +6593,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6622,7 +6626,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651228</v>
+        <v>131651229</v>
       </c>
       <c r="B48" t="n">
         <v>79264</v>
@@ -6660,10 +6664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493283</v>
+        <v>493259</v>
       </c>
       <c r="R48" t="n">
-        <v>7017147</v>
+        <v>7017152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6696,11 +6700,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6753,10 +6752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651229</v>
+        <v>131651189</v>
       </c>
       <c r="B49" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6764,37 +6763,54 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493259</v>
+        <v>493301</v>
       </c>
       <c r="R49" t="n">
-        <v>7017152</v>
+        <v>7016941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6829,39 +6845,23 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -5492,7 +5492,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B39" t="n">
         <v>97903</v>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R39" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B40" t="n">
         <v>97903</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R40" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5706,35 +5706,39 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>80398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,22 +5803,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,10 +5836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651187</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>80398</v>
+        <v>80273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5848,30 +5847,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5879,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493275</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7016819</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5917,6 +5912,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80273</v>
+        <v>91852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R2" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,12 +762,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -785,14 +781,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651232</v>
+        <v>131651174</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,26 +822,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493294</v>
+        <v>493215</v>
       </c>
       <c r="R3" t="n">
-        <v>7016924</v>
+        <v>7016987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,13 +903,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -918,12 +923,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651197</v>
+        <v>131651232</v>
       </c>
       <c r="B4" t="n">
-        <v>80369</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +957,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493219</v>
+        <v>493294</v>
       </c>
       <c r="R4" t="n">
-        <v>7017136</v>
+        <v>7016924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,19 +1052,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651206</v>
+        <v>131651177</v>
       </c>
       <c r="B5" t="n">
-        <v>80405</v>
+        <v>80400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493377</v>
+        <v>493347</v>
       </c>
       <c r="R5" t="n">
-        <v>7017100</v>
+        <v>7017111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651177</v>
+        <v>131651208</v>
       </c>
       <c r="B6" t="n">
-        <v>80398</v>
+        <v>80407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493347</v>
+        <v>493289</v>
       </c>
       <c r="R6" t="n">
-        <v>7017111</v>
+        <v>7016944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651208</v>
+        <v>131651206</v>
       </c>
       <c r="B7" t="n">
-        <v>80405</v>
+        <v>80407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493289</v>
+        <v>493377</v>
       </c>
       <c r="R7" t="n">
-        <v>7016944</v>
+        <v>7017100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651204</v>
+        <v>131651181</v>
       </c>
       <c r="B9" t="n">
-        <v>80405</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,21 +1590,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493221</v>
+        <v>493364</v>
       </c>
       <c r="R9" t="n">
-        <v>7017135</v>
+        <v>7017079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,6 +1659,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1676,12 +1681,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,52 +1714,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B10" t="n">
-        <v>80398</v>
+        <v>58063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R10" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1814,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1809,24 +1822,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,61 +1842,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651176</v>
+        <v>131651204</v>
       </c>
       <c r="B11" t="n">
-        <v>58061</v>
+        <v>80407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493288</v>
+        <v>493221</v>
       </c>
       <c r="R11" t="n">
-        <v>7016960</v>
+        <v>7017135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1933,17 +1922,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1952,9 +1937,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80405</v>
+        <v>80407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651170</v>
+        <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,29 +2499,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2531,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R16" t="n">
-        <v>7017120</v>
+        <v>7017133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2580,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651198</v>
+        <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>80407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493220</v>
+        <v>493230</v>
       </c>
       <c r="R17" t="n">
-        <v>7017133</v>
+        <v>7016768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,11 +2701,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2758,39 +2753,40 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651210</v>
+        <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>80405</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493230</v>
+        <v>493232</v>
       </c>
       <c r="R18" t="n">
-        <v>7016768</v>
+        <v>7017120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2838,13 +2834,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
         <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>80405</v>
+        <v>80407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>131651178</v>
       </c>
       <c r="B21" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>131651172</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651168</v>
+        <v>131651231</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3425,31 +3425,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3457,10 +3452,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493227</v>
+        <v>493312</v>
       </c>
       <c r="R23" t="n">
-        <v>7017123</v>
+        <v>7016962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3497,7 +3492,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3506,6 +3501,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3526,12 +3522,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3549,37 +3545,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>80407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R24" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,11 +3625,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3647,22 +3642,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3680,39 +3675,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651203</v>
+        <v>131651168</v>
       </c>
       <c r="B25" t="n">
-        <v>80405</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3722,10 +3718,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493344</v>
+        <v>493227</v>
       </c>
       <c r="R25" t="n">
-        <v>7017110</v>
+        <v>7017123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3760,13 +3756,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3777,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>131651224</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>131651165</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4332,38 +4332,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651192</v>
+        <v>131651226</v>
       </c>
       <c r="B30" t="n">
-        <v>97903</v>
+        <v>79266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4371,10 +4370,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493258</v>
+        <v>493370</v>
       </c>
       <c r="R30" t="n">
-        <v>7016969</v>
+        <v>7017120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4422,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4439,37 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651226</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>97909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4477,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493370</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7017120</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B32" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R32" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,6 +4643,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4695,10 +4700,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B33" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4737,10 +4742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4773,11 +4778,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4833,7 +4833,7 @@
         <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131651199</v>
       </c>
       <c r="B35" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131651179</v>
       </c>
       <c r="B36" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131651225</v>
+        <v>131651169</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,24 +5237,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493294</v>
+        <v>493230</v>
       </c>
       <c r="R37" t="n">
-        <v>7017032</v>
+        <v>7017123</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5304,7 +5309,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5313,7 +5318,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5339,7 +5343,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131651169</v>
+        <v>131651225</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5368,29 +5372,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5400,10 +5399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493230</v>
+        <v>493294</v>
       </c>
       <c r="R38" t="n">
-        <v>7017123</v>
+        <v>7017032</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5440,7 +5439,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5449,6 +5448,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
         <v>131651193</v>
       </c>
       <c r="B39" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>131651194</v>
       </c>
       <c r="B40" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5706,39 +5706,35 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B41" t="n">
-        <v>80398</v>
+        <v>91858</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5839,7 +5840,7 @@
         <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5967,35 +5968,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>80400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6043,11 +6048,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
         <v>131651222</v>
       </c>
       <c r="B44" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>131651200</v>
       </c>
       <c r="B45" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651202</v>
+        <v>131651228</v>
       </c>
       <c r="B46" t="n">
-        <v>80369</v>
+        <v>79266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493288</v>
+        <v>493283</v>
       </c>
       <c r="R46" t="n">
-        <v>7016954</v>
+        <v>7017147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6462,22 +6462,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651228</v>
+        <v>131651173</v>
       </c>
       <c r="B47" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6506,26 +6506,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6533,10 +6538,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493283</v>
+        <v>493227</v>
       </c>
       <c r="R47" t="n">
-        <v>7017147</v>
+        <v>7017003</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6573,7 +6578,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6582,7 +6587,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6603,12 +6607,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6626,10 +6630,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651229</v>
+        <v>131651202</v>
       </c>
       <c r="B48" t="n">
-        <v>79264</v>
+        <v>80371</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6637,21 +6641,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6664,10 +6668,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493259</v>
+        <v>493288</v>
       </c>
       <c r="R48" t="n">
-        <v>7017152</v>
+        <v>7016954</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6702,6 +6706,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6719,22 +6728,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6752,10 +6761,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651189</v>
+        <v>131651229</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6763,54 +6772,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493301</v>
+        <v>493259</v>
       </c>
       <c r="R49" t="n">
-        <v>7016941</v>
+        <v>7017152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6845,23 +6837,39 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6879,10 +6887,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651173</v>
+        <v>131651189</v>
       </c>
       <c r="B50" t="n">
-        <v>57902</v>
+        <v>57901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6890,16 +6898,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6907,25 +6915,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493227</v>
+        <v>493301</v>
       </c>
       <c r="R50" t="n">
-        <v>7017003</v>
+        <v>7016941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6962,7 +6982,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6977,26 +6997,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
         <v>131651185</v>
       </c>
       <c r="B51" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>131651167</v>
       </c>
       <c r="B52" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -1579,52 +1579,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>58063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R9" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1661,7 +1670,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,7 +1679,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1679,24 +1687,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,61 +1707,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>58063</v>
+        <v>80400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R10" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1789,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,6 +1798,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1822,9 +1807,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2888,37 +2888,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B19" t="n">
-        <v>80407</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2926,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R19" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,13 +2969,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2981,22 +2990,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3014,42 +3023,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>80407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R20" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,17 +3099,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3414,37 +3414,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>80407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R23" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3490,11 +3494,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3512,22 +3511,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,41 +3544,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651203</v>
+        <v>131651231</v>
       </c>
       <c r="B24" t="n">
-        <v>80407</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493344</v>
+        <v>493312</v>
       </c>
       <c r="R24" t="n">
-        <v>7017110</v>
+        <v>7016962</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,6 +3620,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3642,22 +3642,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B32" t="n">
         <v>80400</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R32" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,11 +4643,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4700,7 +4695,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B33" t="n">
         <v>80400</v>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R33" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4778,6 +4773,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131651169</v>
+        <v>131651225</v>
       </c>
       <c r="B37" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,29 +5237,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493230</v>
+        <v>493294</v>
       </c>
       <c r="R37" t="n">
-        <v>7017123</v>
+        <v>7017032</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5309,7 +5304,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5318,6 +5313,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5343,7 +5339,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5361,10 +5357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131651225</v>
+        <v>131651169</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5372,24 +5368,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5399,10 +5400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493294</v>
+        <v>493230</v>
       </c>
       <c r="R38" t="n">
-        <v>7017032</v>
+        <v>7017123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5439,7 +5440,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5448,7 +5449,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5706,37 +5706,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>80275</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R41" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5804,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,37 +5837,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B42" t="n">
-        <v>80275</v>
+        <v>91858</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,22 +5935,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651228</v>
+        <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>79266</v>
+        <v>80371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493283</v>
+        <v>493288</v>
       </c>
       <c r="R46" t="n">
-        <v>7017147</v>
+        <v>7016954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6462,22 +6462,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6495,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651173</v>
+        <v>131651229</v>
       </c>
       <c r="B47" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6506,31 +6506,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6538,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493227</v>
+        <v>493259</v>
       </c>
       <c r="R47" t="n">
-        <v>7017003</v>
+        <v>7017152</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6576,17 +6571,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6607,12 +6598,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6630,10 +6621,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651202</v>
+        <v>131651189</v>
       </c>
       <c r="B48" t="n">
-        <v>80371</v>
+        <v>57901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6641,37 +6632,54 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493288</v>
+        <v>493301</v>
       </c>
       <c r="R48" t="n">
-        <v>7016954</v>
+        <v>7016941</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6708,7 +6716,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6717,33 +6725,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6761,7 +6748,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651229</v>
+        <v>131651228</v>
       </c>
       <c r="B49" t="n">
         <v>79266</v>
@@ -6799,10 +6786,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493259</v>
+        <v>493283</v>
       </c>
       <c r="R49" t="n">
-        <v>7017152</v>
+        <v>7017147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6835,6 +6822,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6887,10 +6879,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651189</v>
+        <v>131651173</v>
       </c>
       <c r="B50" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6898,16 +6890,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6915,37 +6907,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493301</v>
+        <v>493227</v>
       </c>
       <c r="R50" t="n">
-        <v>7016941</v>
+        <v>7017003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6982,7 +6962,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6997,6 +6977,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -1579,61 +1579,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B9" t="n">
-        <v>58063</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R9" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1670,7 +1661,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,6 +1670,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1687,9 +1679,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,52 +1714,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B10" t="n">
-        <v>80400</v>
+        <v>58063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R10" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,7 +1814,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1807,24 +1822,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131651207</v>
+        <v>131651182</v>
       </c>
       <c r="B14" t="n">
-        <v>80407</v>
+        <v>80400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493289</v>
+        <v>493263</v>
       </c>
       <c r="R14" t="n">
-        <v>7016938</v>
+        <v>7016993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131651182</v>
+        <v>131651207</v>
       </c>
       <c r="B15" t="n">
-        <v>80400</v>
+        <v>80407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493263</v>
+        <v>493289</v>
       </c>
       <c r="R15" t="n">
-        <v>7016993</v>
+        <v>7016938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2888,42 +2888,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>80407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2931,10 +2926,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R19" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,17 +2964,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2990,22 +2981,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3023,37 +3014,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>80407</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3061,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R20" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3099,13 +3095,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3414,41 +3414,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651203</v>
+        <v>131651231</v>
       </c>
       <c r="B23" t="n">
-        <v>80407</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3456,10 +3452,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493344</v>
+        <v>493312</v>
       </c>
       <c r="R23" t="n">
-        <v>7017110</v>
+        <v>7016962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3494,6 +3490,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3511,22 +3512,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3544,37 +3545,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>80407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R24" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3620,11 +3625,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3642,22 +3642,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B32" t="n">
         <v>80400</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R32" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,6 +4643,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4695,7 +4700,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B33" t="n">
         <v>80400</v>
@@ -4737,10 +4742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4773,11 +4778,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>80275</v>
+        <v>80400</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5717,26 +5717,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,12 +5803,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5819,7 +5818,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,37 +5836,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>80275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5875,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5915,7 +5914,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,22 +5934,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,39 +5967,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80400</v>
+        <v>91858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,6 +6043,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -1579,52 +1579,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>58063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R9" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1661,7 +1670,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,7 +1679,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1679,24 +1687,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,61 +1707,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>58063</v>
+        <v>80400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R10" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,7 +1789,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,6 +1798,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1822,9 +1807,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B32" t="n">
         <v>80400</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R32" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,11 +4643,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4700,7 +4695,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B33" t="n">
         <v>80400</v>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R33" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4778,6 +4773,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -4071,37 +4071,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651224</v>
+        <v>131651192</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>97909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4109,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493343</v>
+        <v>493258</v>
       </c>
       <c r="R28" t="n">
-        <v>7017125</v>
+        <v>7016969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4147,11 +4148,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4165,26 +4161,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4332,10 +4308,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651226</v>
+        <v>131651224</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4343,26 +4319,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4370,10 +4346,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493370</v>
+        <v>493343</v>
       </c>
       <c r="R30" t="n">
-        <v>7017120</v>
+        <v>7017125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4408,6 +4384,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4435,12 +4416,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,38 +4439,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651192</v>
+        <v>131651226</v>
       </c>
       <c r="B31" t="n">
-        <v>97909</v>
+        <v>79266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4497,10 +4477,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493258</v>
+        <v>493370</v>
       </c>
       <c r="R31" t="n">
-        <v>7016969</v>
+        <v>7017120</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4548,6 +4528,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651190</v>
       </c>
       <c r="B41" t="n">
-        <v>80400</v>
+        <v>80275</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5717,30 +5717,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493279</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7016965</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,12 +5804,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5818,7 +5819,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,37 +5837,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B42" t="n">
-        <v>80275</v>
+        <v>91858</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5914,7 +5915,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5934,22 +5935,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,35 +5968,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>80400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6043,11 +6048,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651177</v>
+        <v>131651208</v>
       </c>
       <c r="B5" t="n">
-        <v>80400</v>
+        <v>80407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493347</v>
+        <v>493289</v>
       </c>
       <c r="R5" t="n">
-        <v>7017111</v>
+        <v>7016944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651208</v>
+        <v>131651206</v>
       </c>
       <c r="B6" t="n">
         <v>80407</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493289</v>
+        <v>493377</v>
       </c>
       <c r="R6" t="n">
-        <v>7016944</v>
+        <v>7017100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651206</v>
+        <v>131651177</v>
       </c>
       <c r="B7" t="n">
-        <v>80407</v>
+        <v>80400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493377</v>
+        <v>493347</v>
       </c>
       <c r="R7" t="n">
-        <v>7017100</v>
+        <v>7017111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131651182</v>
+        <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80400</v>
+        <v>80407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493263</v>
+        <v>493289</v>
       </c>
       <c r="R14" t="n">
-        <v>7016993</v>
+        <v>7016938</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131651207</v>
+        <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80407</v>
+        <v>80400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493289</v>
+        <v>493263</v>
       </c>
       <c r="R15" t="n">
-        <v>7016938</v>
+        <v>7016993</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2888,37 +2888,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B19" t="n">
-        <v>80407</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2926,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R19" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,13 +2969,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2981,22 +2990,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3014,42 +3023,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>80407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R20" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,17 +3099,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -4071,38 +4071,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651192</v>
+        <v>131651224</v>
       </c>
       <c r="B28" t="n">
-        <v>97909</v>
+        <v>91858</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4110,10 +4109,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493258</v>
+        <v>493343</v>
       </c>
       <c r="R28" t="n">
-        <v>7016969</v>
+        <v>7017125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4148,6 +4147,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4161,6 +4165,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4308,10 +4332,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651224</v>
+        <v>131651226</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4319,26 +4343,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4346,10 +4370,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493343</v>
+        <v>493370</v>
       </c>
       <c r="R30" t="n">
-        <v>7017125</v>
+        <v>7017120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4384,11 +4408,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4416,12 +4435,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4439,37 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651226</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>97909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4477,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493370</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7017120</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131651225</v>
+        <v>131651169</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,24 +5237,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493294</v>
+        <v>493230</v>
       </c>
       <c r="R37" t="n">
-        <v>7017032</v>
+        <v>7017123</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5304,7 +5309,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5313,7 +5318,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5339,7 +5343,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131651169</v>
+        <v>131651225</v>
       </c>
       <c r="B38" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5368,29 +5372,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5400,10 +5399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493230</v>
+        <v>493294</v>
       </c>
       <c r="R38" t="n">
-        <v>7017123</v>
+        <v>7017032</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5440,7 +5439,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5449,6 +5448,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>80275</v>
+        <v>80400</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5717,26 +5717,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,12 +5803,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5819,7 +5818,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,37 +5836,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>80275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5875,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5915,7 +5914,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,22 +5934,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,39 +5967,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80400</v>
+        <v>91858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,6 +6043,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651202</v>
+        <v>131651189</v>
       </c>
       <c r="B46" t="n">
-        <v>80371</v>
+        <v>57901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,37 +6375,54 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493288</v>
+        <v>493301</v>
       </c>
       <c r="R46" t="n">
-        <v>7016954</v>
+        <v>7016941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6442,7 +6459,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6451,33 +6468,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6495,10 +6491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651229</v>
+        <v>131651202</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>80371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6506,21 +6502,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6533,10 +6529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493259</v>
+        <v>493288</v>
       </c>
       <c r="R47" t="n">
-        <v>7017152</v>
+        <v>7016954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6571,6 +6567,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6588,22 +6589,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6621,10 +6622,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651189</v>
+        <v>131651228</v>
       </c>
       <c r="B48" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6632,54 +6633,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493301</v>
+        <v>493283</v>
       </c>
       <c r="R48" t="n">
-        <v>7016941</v>
+        <v>7017147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6716,7 +6700,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6725,12 +6709,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6748,7 +6753,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651228</v>
+        <v>131651229</v>
       </c>
       <c r="B49" t="n">
         <v>79266</v>
@@ -6786,10 +6791,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493283</v>
+        <v>493259</v>
       </c>
       <c r="R49" t="n">
-        <v>7017147</v>
+        <v>7017152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6822,11 +6827,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651208</v>
+        <v>131651177</v>
       </c>
       <c r="B5" t="n">
-        <v>80407</v>
+        <v>80400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493289</v>
+        <v>493347</v>
       </c>
       <c r="R5" t="n">
-        <v>7016944</v>
+        <v>7017111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651206</v>
+        <v>131651208</v>
       </c>
       <c r="B6" t="n">
         <v>80407</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493377</v>
+        <v>493289</v>
       </c>
       <c r="R6" t="n">
-        <v>7017100</v>
+        <v>7016944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651177</v>
+        <v>131651206</v>
       </c>
       <c r="B7" t="n">
-        <v>80400</v>
+        <v>80407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493347</v>
+        <v>493377</v>
       </c>
       <c r="R7" t="n">
-        <v>7017111</v>
+        <v>7017100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1579,61 +1579,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B9" t="n">
-        <v>58063</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R9" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1670,7 +1661,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,6 +1670,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1687,9 +1679,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,52 +1714,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B10" t="n">
-        <v>80400</v>
+        <v>58063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R10" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,7 +1814,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1807,24 +1822,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131651207</v>
+        <v>131651182</v>
       </c>
       <c r="B14" t="n">
-        <v>80407</v>
+        <v>80400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493289</v>
+        <v>493263</v>
       </c>
       <c r="R14" t="n">
-        <v>7016938</v>
+        <v>7016993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131651182</v>
+        <v>131651207</v>
       </c>
       <c r="B15" t="n">
-        <v>80400</v>
+        <v>80407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493263</v>
+        <v>493289</v>
       </c>
       <c r="R15" t="n">
-        <v>7016993</v>
+        <v>7016938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2888,42 +2888,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>80407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2931,10 +2926,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R19" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,17 +2964,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2990,22 +2981,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3023,37 +3014,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>80407</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3061,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R20" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3099,13 +3095,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -4071,37 +4071,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651224</v>
+        <v>131651192</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>97909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4109,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493343</v>
+        <v>493258</v>
       </c>
       <c r="R28" t="n">
-        <v>7017125</v>
+        <v>7016969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4147,11 +4148,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4165,26 +4161,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4332,10 +4308,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651226</v>
+        <v>131651224</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4343,26 +4319,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4370,10 +4346,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493370</v>
+        <v>493343</v>
       </c>
       <c r="R30" t="n">
-        <v>7017120</v>
+        <v>7017125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4408,6 +4384,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4435,12 +4416,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,38 +4439,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651192</v>
+        <v>131651226</v>
       </c>
       <c r="B31" t="n">
-        <v>97909</v>
+        <v>79266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4497,10 +4477,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493258</v>
+        <v>493370</v>
       </c>
       <c r="R31" t="n">
-        <v>7016969</v>
+        <v>7017120</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4548,6 +4528,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B32" t="n">
         <v>80400</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R32" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,6 +4643,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4695,7 +4700,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B33" t="n">
         <v>80400</v>
@@ -4737,10 +4742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4773,11 +4778,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651190</v>
       </c>
       <c r="B41" t="n">
-        <v>80400</v>
+        <v>80275</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5717,30 +5717,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493279</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7016965</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,12 +5804,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5818,7 +5819,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,37 +5837,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B42" t="n">
-        <v>80275</v>
+        <v>91858</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5914,7 +5915,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5934,22 +5935,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,35 +5968,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>80400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6043,11 +6048,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651189</v>
+        <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>57901</v>
+        <v>80371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,54 +6375,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493301</v>
+        <v>493288</v>
       </c>
       <c r="R46" t="n">
-        <v>7016941</v>
+        <v>7016954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6459,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6468,12 +6451,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6491,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651202</v>
+        <v>131651229</v>
       </c>
       <c r="B47" t="n">
-        <v>80371</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6502,21 +6506,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6529,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493288</v>
+        <v>493259</v>
       </c>
       <c r="R47" t="n">
-        <v>7016954</v>
+        <v>7017152</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6567,11 +6571,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6589,22 +6588,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6622,10 +6621,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651228</v>
+        <v>131651189</v>
       </c>
       <c r="B48" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6633,37 +6632,54 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493283</v>
+        <v>493301</v>
       </c>
       <c r="R48" t="n">
-        <v>7017147</v>
+        <v>7016941</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6700,7 +6716,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6709,33 +6725,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6753,7 +6748,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651229</v>
+        <v>131651228</v>
       </c>
       <c r="B49" t="n">
         <v>79266</v>
@@ -6791,10 +6786,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493259</v>
+        <v>493283</v>
       </c>
       <c r="R49" t="n">
-        <v>7017152</v>
+        <v>7017147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6827,6 +6822,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7014,39 +7014,40 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131651185</v>
+        <v>131651167</v>
       </c>
       <c r="B51" t="n">
-        <v>80400</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7056,10 +7057,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493234</v>
+        <v>493229</v>
       </c>
       <c r="R51" t="n">
-        <v>7016744</v>
+        <v>7017129</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7094,13 +7095,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död delvis avbarkad gran med äldre sannolika födosökspår av tretåig hackspett. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7111,22 +7116,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7144,40 +7149,39 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131651167</v>
+        <v>131651185</v>
       </c>
       <c r="B52" t="n">
-        <v>57904</v>
+        <v>80400</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7187,10 +7191,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493229</v>
+        <v>493234</v>
       </c>
       <c r="R52" t="n">
-        <v>7017129</v>
+        <v>7016744</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7225,17 +7229,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död delvis avbarkad gran med äldre sannolika födosökspår av tretåig hackspett. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7246,22 +7246,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131651197</v>
+        <v>131651232</v>
       </c>
       <c r="B2" t="n">
-        <v>80371</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493219</v>
+        <v>493294</v>
       </c>
       <c r="R2" t="n">
-        <v>7017136</v>
+        <v>7016924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,19 +781,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>80374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,31 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R3" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,12 +893,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -921,14 +912,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651232</v>
+        <v>131651174</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,26 +953,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493294</v>
+        <v>493215</v>
       </c>
       <c r="R4" t="n">
-        <v>7016924</v>
+        <v>7016987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,13 +1034,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651177</v>
+        <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>80400</v>
+        <v>80410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493347</v>
+        <v>493377</v>
       </c>
       <c r="R5" t="n">
-        <v>7017111</v>
+        <v>7017100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651208</v>
+        <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80407</v>
+        <v>80403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493289</v>
+        <v>493347</v>
       </c>
       <c r="R6" t="n">
-        <v>7016944</v>
+        <v>7017111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651206</v>
+        <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493377</v>
+        <v>493289</v>
       </c>
       <c r="R7" t="n">
-        <v>7017100</v>
+        <v>7016944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,52 +1579,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>58066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R9" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1661,7 +1670,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,7 +1679,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1679,24 +1687,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,61 +1707,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651176</v>
+        <v>131651204</v>
       </c>
       <c r="B10" t="n">
-        <v>58063</v>
+        <v>80410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493288</v>
+        <v>493221</v>
       </c>
       <c r="R10" t="n">
-        <v>7016960</v>
+        <v>7017135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1803,17 +1787,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1822,9 +1802,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651204</v>
+        <v>131651181</v>
       </c>
       <c r="B11" t="n">
-        <v>80407</v>
+        <v>80403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1884,10 +1879,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493221</v>
+        <v>493364</v>
       </c>
       <c r="R11" t="n">
-        <v>7017135</v>
+        <v>7017079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1922,6 +1917,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131651182</v>
+        <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80400</v>
+        <v>80410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493263</v>
+        <v>493289</v>
       </c>
       <c r="R14" t="n">
-        <v>7016993</v>
+        <v>7016938</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131651207</v>
+        <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80407</v>
+        <v>80403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493289</v>
+        <v>493263</v>
       </c>
       <c r="R15" t="n">
-        <v>7016938</v>
+        <v>7016993</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
         <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>131651178</v>
       </c>
       <c r="B21" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>131651172</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>131651231</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>131651203</v>
       </c>
       <c r="B24" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>131651168</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>131651192</v>
       </c>
       <c r="B28" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>131651165</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>131651224</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>131651226</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B32" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R32" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4643,11 +4643,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4700,10 +4695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651184</v>
+        <v>131651183</v>
       </c>
       <c r="B33" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493261</v>
+        <v>493286</v>
       </c>
       <c r="R33" t="n">
-        <v>7016936</v>
+        <v>7016955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4778,6 +4773,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4833,7 +4833,7 @@
         <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131651199</v>
       </c>
       <c r="B35" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131651179</v>
       </c>
       <c r="B36" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131651169</v>
       </c>
       <c r="B37" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>131651225</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B39" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R39" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B40" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R40" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>80275</v>
+        <v>80403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5717,26 +5717,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,12 +5803,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5819,7 +5818,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,37 +5836,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>80278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5875,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5915,7 +5914,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,22 +5934,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,39 +5967,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80400</v>
+        <v>91861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,6 +6043,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
         <v>131651222</v>
       </c>
       <c r="B44" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>131651200</v>
       </c>
       <c r="B45" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6495,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651229</v>
+        <v>131651228</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493259</v>
+        <v>493283</v>
       </c>
       <c r="R47" t="n">
-        <v>7017152</v>
+        <v>7017147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6569,6 +6569,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651189</v>
+        <v>131651229</v>
       </c>
       <c r="B48" t="n">
-        <v>57901</v>
+        <v>79269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6632,54 +6637,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493301</v>
+        <v>493259</v>
       </c>
       <c r="R48" t="n">
-        <v>7016941</v>
+        <v>7017152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6714,23 +6702,39 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6748,10 +6752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651228</v>
+        <v>131651173</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6759,26 +6763,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6786,10 +6795,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493283</v>
+        <v>493227</v>
       </c>
       <c r="R49" t="n">
-        <v>7017147</v>
+        <v>7017003</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6826,7 +6835,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6835,7 +6844,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6856,12 +6864,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6879,7 +6887,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651173</v>
+        <v>131651189</v>
       </c>
       <c r="B50" t="n">
         <v>57904</v>
@@ -6890,16 +6898,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6907,25 +6915,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493227</v>
+        <v>493301</v>
       </c>
       <c r="R50" t="n">
-        <v>7017003</v>
+        <v>7016941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6962,7 +6982,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6977,26 +6997,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
         <v>131651167</v>
       </c>
       <c r="B51" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>131651185</v>
       </c>
       <c r="B52" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131651232</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131651197</v>
       </c>
       <c r="B3" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>131651174</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,61 +1579,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651176</v>
+        <v>131651204</v>
       </c>
       <c r="B9" t="n">
-        <v>58066</v>
+        <v>80415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493288</v>
+        <v>493221</v>
       </c>
       <c r="R9" t="n">
-        <v>7016960</v>
+        <v>7017135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,17 +1659,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1687,9 +1674,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651204</v>
+        <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>80410</v>
+        <v>80408</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,21 +1720,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1749,10 +1751,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493221</v>
+        <v>493364</v>
       </c>
       <c r="R10" t="n">
-        <v>7017135</v>
+        <v>7017079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1787,6 +1789,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1804,12 +1811,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1819,7 +1826,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1837,52 +1844,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B11" t="n">
-        <v>80403</v>
+        <v>58071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R11" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1935,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1928,7 +1944,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1937,24 +1952,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B16" t="n">
-        <v>80374</v>
+        <v>57912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,28 +2499,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2530,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R16" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2571,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2580,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,32 +2623,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B17" t="n">
-        <v>80410</v>
+        <v>80379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R17" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,6 +2701,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,40 +2758,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B18" t="n">
-        <v>57907</v>
+        <v>80415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R18" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,17 +2838,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
         <v>131651209</v>
       </c>
       <c r="B19" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131651171</v>
       </c>
       <c r="B20" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3149,39 +3149,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131651178</v>
+        <v>131651172</v>
       </c>
       <c r="B21" t="n">
-        <v>80403</v>
+        <v>57912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493301</v>
+        <v>493291</v>
       </c>
       <c r="R21" t="n">
-        <v>7017157</v>
+        <v>7017105</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3229,13 +3230,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3246,22 +3251,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3279,40 +3284,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131651172</v>
+        <v>131651178</v>
       </c>
       <c r="B22" t="n">
-        <v>57907</v>
+        <v>80408</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3322,10 +3326,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493291</v>
+        <v>493301</v>
       </c>
       <c r="R22" t="n">
-        <v>7017105</v>
+        <v>7017157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3360,17 +3364,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3414,37 +3414,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651231</v>
+        <v>131651203</v>
       </c>
       <c r="B23" t="n">
-        <v>79269</v>
+        <v>80415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493312</v>
+        <v>493344</v>
       </c>
       <c r="R23" t="n">
-        <v>7016962</v>
+        <v>7017110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3490,11 +3494,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3512,22 +3511,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,39 +3544,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651203</v>
+        <v>131651168</v>
       </c>
       <c r="B24" t="n">
-        <v>80410</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493344</v>
+        <v>493227</v>
       </c>
       <c r="R24" t="n">
-        <v>7017110</v>
+        <v>7017123</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,13 +3625,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3642,22 +3646,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,10 +3679,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651168</v>
+        <v>131651231</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,31 +3690,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3718,10 +3717,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493227</v>
+        <v>493312</v>
       </c>
       <c r="R25" t="n">
-        <v>7017123</v>
+        <v>7016962</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3758,7 +3757,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3767,6 +3766,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4071,38 +4071,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131651192</v>
+        <v>131651165</v>
       </c>
       <c r="B28" t="n">
-        <v>97912</v>
+        <v>91846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4110,10 +4113,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493258</v>
+        <v>493266</v>
       </c>
       <c r="R28" t="n">
-        <v>7016969</v>
+        <v>7016915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4161,6 +4164,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4178,10 +4201,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131651165</v>
+        <v>131651224</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>91866</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4189,23 +4212,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -4220,10 +4239,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493266</v>
+        <v>493343</v>
       </c>
       <c r="R29" t="n">
-        <v>7016915</v>
+        <v>7017125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4258,6 +4277,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4285,12 +4309,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4308,10 +4332,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131651224</v>
+        <v>131651226</v>
       </c>
       <c r="B30" t="n">
-        <v>91861</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4319,26 +4343,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4346,10 +4370,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493343</v>
+        <v>493370</v>
       </c>
       <c r="R30" t="n">
-        <v>7017125</v>
+        <v>7017120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4384,11 +4408,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med hackspår av hackspett (försök till bohål) på låg höjd).</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4416,12 +4435,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4439,37 +4458,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131651226</v>
+        <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>79269</v>
+        <v>97917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4477,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493370</v>
+        <v>493258</v>
       </c>
       <c r="R31" t="n">
-        <v>7017120</v>
+        <v>7016969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4528,26 +4548,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
         <v>131651184</v>
       </c>
       <c r="B32" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>131651183</v>
       </c>
       <c r="B33" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>131651196</v>
       </c>
       <c r="B34" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>131651199</v>
       </c>
       <c r="B35" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131651179</v>
       </c>
       <c r="B36" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131651169</v>
       </c>
       <c r="B37" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>131651225</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131651194</v>
+        <v>131651193</v>
       </c>
       <c r="B39" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493237</v>
+        <v>493272</v>
       </c>
       <c r="R39" t="n">
-        <v>7016939</v>
+        <v>7016833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131651193</v>
+        <v>131651194</v>
       </c>
       <c r="B40" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493272</v>
+        <v>493237</v>
       </c>
       <c r="R40" t="n">
-        <v>7016833</v>
+        <v>7016939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5709,7 +5709,7 @@
         <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131651222</v>
+        <v>131651200</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>80379</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6109,30 +6109,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6140,10 +6136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R44" t="n">
-        <v>7016908</v>
+        <v>7017008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6180,7 +6176,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6195,27 +6191,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6233,10 +6229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131651200</v>
+        <v>131651222</v>
       </c>
       <c r="B45" t="n">
-        <v>80374</v>
+        <v>91842</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6244,26 +6240,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R45" t="n">
-        <v>7017008</v>
+        <v>7016908</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651202</v>
+        <v>131651189</v>
       </c>
       <c r="B46" t="n">
-        <v>80374</v>
+        <v>57909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,37 +6375,54 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493288</v>
+        <v>493301</v>
       </c>
       <c r="R46" t="n">
-        <v>7016954</v>
+        <v>7016941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6442,7 +6459,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6451,33 +6468,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6495,10 +6491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651228</v>
+        <v>131651173</v>
       </c>
       <c r="B47" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6506,26 +6502,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6533,10 +6534,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493283</v>
+        <v>493227</v>
       </c>
       <c r="R47" t="n">
-        <v>7017147</v>
+        <v>7017003</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6573,7 +6574,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6582,7 +6583,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6603,12 +6603,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651229</v>
+        <v>131651202</v>
       </c>
       <c r="B48" t="n">
-        <v>79269</v>
+        <v>80379</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493259</v>
+        <v>493288</v>
       </c>
       <c r="R48" t="n">
-        <v>7017152</v>
+        <v>7016954</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6702,6 +6702,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6719,22 +6724,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6752,10 +6757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651173</v>
+        <v>131651228</v>
       </c>
       <c r="B49" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6763,31 +6768,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493227</v>
+        <v>493283</v>
       </c>
       <c r="R49" t="n">
-        <v>7017003</v>
+        <v>7017147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6844,6 +6844,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6864,12 +6865,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6887,10 +6888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651189</v>
+        <v>131651229</v>
       </c>
       <c r="B50" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6898,54 +6899,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493301</v>
+        <v>493259</v>
       </c>
       <c r="R50" t="n">
-        <v>7016941</v>
+        <v>7017152</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6980,23 +6964,39 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
         <v>131651167</v>
       </c>
       <c r="B51" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>131651185</v>
       </c>
       <c r="B52" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651197</v>
+        <v>131651174</v>
       </c>
       <c r="B3" t="n">
-        <v>80379</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +817,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493219</v>
+        <v>493215</v>
       </c>
       <c r="R3" t="n">
-        <v>7017136</v>
+        <v>7016987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,13 +898,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -912,19 +916,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>80379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,31 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R4" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,12 +1028,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1052,14 +1047,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651206</v>
+        <v>131651191</v>
       </c>
       <c r="B5" t="n">
-        <v>80415</v>
+        <v>97917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,30 +1088,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493377</v>
+        <v>493254</v>
       </c>
       <c r="R5" t="n">
-        <v>7017100</v>
+        <v>7017114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,24 +1169,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651177</v>
+        <v>131651206</v>
       </c>
       <c r="B6" t="n">
-        <v>80408</v>
+        <v>80415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1200,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1249,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493347</v>
+        <v>493377</v>
       </c>
       <c r="R6" t="n">
-        <v>7017111</v>
+        <v>7017100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651208</v>
+        <v>131651177</v>
       </c>
       <c r="B7" t="n">
-        <v>80415</v>
+        <v>80408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,21 +1330,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1379,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493289</v>
+        <v>493347</v>
       </c>
       <c r="R7" t="n">
-        <v>7016944</v>
+        <v>7017111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1467,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651191</v>
+        <v>131651208</v>
       </c>
       <c r="B8" t="n">
-        <v>97917</v>
+        <v>80415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1460,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1506,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493254</v>
+        <v>493289</v>
       </c>
       <c r="R8" t="n">
-        <v>7017114</v>
+        <v>7016944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,9 +1544,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,52 +1579,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651204</v>
+        <v>131651176</v>
       </c>
       <c r="B9" t="n">
-        <v>80415</v>
+        <v>58071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493221</v>
+        <v>493288</v>
       </c>
       <c r="R9" t="n">
-        <v>7017135</v>
+        <v>7016960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,13 +1668,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1674,24 +1687,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651181</v>
+        <v>131651204</v>
       </c>
       <c r="B10" t="n">
-        <v>80408</v>
+        <v>80415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,21 +1718,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1751,10 +1749,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493364</v>
+        <v>493221</v>
       </c>
       <c r="R10" t="n">
-        <v>7017079</v>
+        <v>7017135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,11 +1787,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en klen rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1811,12 +1804,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1826,7 +1819,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,61 +1837,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651176</v>
+        <v>131651181</v>
       </c>
       <c r="B11" t="n">
-        <v>58071</v>
+        <v>80408</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493288</v>
+        <v>493364</v>
       </c>
       <c r="R11" t="n">
-        <v>7016960</v>
+        <v>7017079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1919,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+          <t>På en klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,6 +1928,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1952,9 +1937,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2488,40 +2488,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B16" t="n">
-        <v>57912</v>
+        <v>80415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2531,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R16" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2569,17 +2568,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2585,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2618,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B17" t="n">
-        <v>80379</v>
+        <v>57912</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,28 +2629,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2665,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R17" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2705,7 +2701,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,7 +2710,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2725,22 +2720,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2758,32 +2753,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B18" t="n">
-        <v>80415</v>
+        <v>80379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2800,10 +2795,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R18" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2836,6 +2831,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5706,39 +5706,35 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651187</v>
+        <v>131651223</v>
       </c>
       <c r="B41" t="n">
-        <v>80408</v>
+        <v>91866</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5748,10 +5744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493275</v>
+        <v>493368</v>
       </c>
       <c r="R41" t="n">
-        <v>7016819</v>
+        <v>7017102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5786,6 +5782,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I en relativt grov döende gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5803,22 +5804,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5836,10 +5837,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651190</v>
+        <v>131651187</v>
       </c>
       <c r="B42" t="n">
-        <v>80283</v>
+        <v>80408</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5847,26 +5848,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5874,10 +5879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493279</v>
+        <v>493275</v>
       </c>
       <c r="R42" t="n">
-        <v>7016965</v>
+        <v>7016819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5912,11 +5917,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651223</v>
+        <v>131651190</v>
       </c>
       <c r="B43" t="n">
-        <v>91866</v>
+        <v>80283</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493368</v>
+        <v>493279</v>
       </c>
       <c r="R43" t="n">
-        <v>7017102</v>
+        <v>7016965</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>I en relativt grov döende gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 8607-2026 artfynd.xlsx
+++ b/artfynd/A 8607-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131651232</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131651174</v>
+        <v>131651197</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>80381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,31 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493215</v>
+        <v>493219</v>
       </c>
       <c r="R3" t="n">
-        <v>7016987</v>
+        <v>7017136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +893,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -916,14 +912,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En klen undertryckt död gran.</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131651197</v>
+        <v>131651174</v>
       </c>
       <c r="B4" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +953,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493219</v>
+        <v>493215</v>
       </c>
       <c r="R4" t="n">
-        <v>7017136</v>
+        <v>7016987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen undertryckt död gran vid en lunglavssälg.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,13 +1034,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,19 +1052,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>En klen undertryckt död gran.</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En klen undertryckt död gran.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131651191</v>
+        <v>131651206</v>
       </c>
       <c r="B5" t="n">
-        <v>97917</v>
+        <v>80417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,27 +1088,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1116,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493254</v>
+        <v>493377</v>
       </c>
       <c r="R5" t="n">
-        <v>7017114</v>
+        <v>7017100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1169,9 +1172,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131651206</v>
+        <v>131651177</v>
       </c>
       <c r="B6" t="n">
-        <v>80415</v>
+        <v>80410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1231,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493377</v>
+        <v>493347</v>
       </c>
       <c r="R6" t="n">
-        <v>7017100</v>
+        <v>7017111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1319,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131651177</v>
+        <v>131651208</v>
       </c>
       <c r="B7" t="n">
-        <v>80408</v>
+        <v>80417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,21 +1348,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1361,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493347</v>
+        <v>493289</v>
       </c>
       <c r="R7" t="n">
-        <v>7017111</v>
+        <v>7016944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1449,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131651208</v>
+        <v>131651191</v>
       </c>
       <c r="B8" t="n">
-        <v>80415</v>
+        <v>97919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,30 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1491,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493289</v>
+        <v>493254</v>
       </c>
       <c r="R8" t="n">
-        <v>7016944</v>
+        <v>7017114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,24 +1559,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,61 +1579,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131651176</v>
+        <v>131651204</v>
       </c>
       <c r="B9" t="n">
-        <v>58071</v>
+        <v>80417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493288</v>
+        <v>493221</v>
       </c>
       <c r="R9" t="n">
-        <v>7016960</v>
+        <v>7017135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,17 +1659,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1687,9 +1674,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131651204</v>
+        <v>131651181</v>
       </c>
       <c r="B10" t="n">
-        <v>80415</v>
+        <v>80410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,21 +1720,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1749,10 +1751,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493221</v>
+        <v>493364</v>
       </c>
       <c r="R10" t="n">
-        <v>7017135</v>
+        <v>7017079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1787,6 +1789,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en klen rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1804,12 +1811,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1819,7 +1826,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1837,52 +1844,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131651181</v>
+        <v>131651176</v>
       </c>
       <c r="B11" t="n">
-        <v>80408</v>
+        <v>58073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493364</v>
+        <v>493288</v>
       </c>
       <c r="R11" t="n">
-        <v>7017079</v>
+        <v>7016960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1935,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en klen rönn.</t>
+          <t>Minst 2 talltitor observerades i bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1928,7 +1944,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1937,24 +1952,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av tall, björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>131651195</v>
       </c>
       <c r="B12" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131651230</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>131651207</v>
       </c>
       <c r="B14" t="n">
-        <v>80415</v>
+        <v>80417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>131651182</v>
       </c>
       <c r="B15" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,32 +2488,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131651210</v>
+        <v>131651198</v>
       </c>
       <c r="B16" t="n">
-        <v>80415</v>
+        <v>80381</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493230</v>
+        <v>493220</v>
       </c>
       <c r="R16" t="n">
-        <v>7016768</v>
+        <v>7017133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2566,6 +2566,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2618,40 +2623,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131651170</v>
+        <v>131651210</v>
       </c>
       <c r="B17" t="n">
-        <v>57912</v>
+        <v>80417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2661,10 +2665,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493232</v>
+        <v>493230</v>
       </c>
       <c r="R17" t="n">
-        <v>7017120</v>
+        <v>7016768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2699,17 +2703,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2720,22 +2720,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131651198</v>
+        <v>131651170</v>
       </c>
       <c r="B18" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2764,28 +2764,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2795,10 +2796,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R18" t="n">
-        <v>7017133</v>
+        <v>7017120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2835,7 +2836,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I riklig mängd på en sälg. Fertil med apothecier.</t>
+          <t>Ringhack (savhack), färska, på en något smalare gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2844,7 +2845,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2855,22 +2855,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2888,37 +2888,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131651209</v>
+        <v>131651171</v>
       </c>
       <c r="B19" t="n">
-        <v>80415</v>
+        <v>57914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2926,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493280</v>
+        <v>493262</v>
       </c>
       <c r="R19" t="n">
-        <v>7016965</v>
+        <v>7017114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,13 +2969,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2981,22 +2990,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3014,42 +3023,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131651171</v>
+        <v>131651209</v>
       </c>
       <c r="B20" t="n">
-        <v>57912</v>
+        <v>80417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493262</v>
+        <v>493280</v>
       </c>
       <c r="R20" t="n">
-        <v>7017114</v>
+        <v>7016965</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,17 +3099,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran intill en myrstack vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3116,22 +3116,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3152,7 +3152,7 @@
         <v>131651172</v>
       </c>
       <c r="B21" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131651178</v>
       </c>
       <c r="B22" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3414,41 +3414,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131651203</v>
+        <v>131651231</v>
       </c>
       <c r="B23" t="n">
-        <v>80415</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3456,10 +3452,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493344</v>
+        <v>493312</v>
       </c>
       <c r="R23" t="n">
-        <v>7017110</v>
+        <v>7016962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3494,6 +3490,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3511,22 +3512,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3544,40 +3545,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131651168</v>
+        <v>131651203</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>80417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493227</v>
+        <v>493344</v>
       </c>
       <c r="R24" t="n">
-        <v>7017123</v>
+        <v>7017110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3625,17 +3625,13 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3646,22 +3642,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3679,10 +3675,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131651231</v>
+        <v>131651168</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3690,26 +3686,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3717,10 +3718,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493312</v>
+        <v>493227</v>
       </c>
       <c r="R25" t="n">
-        <v>7016962</v>
+        <v>7017123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,7 +3758,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran. Upp till 40 cm bållängd.</t>
+          <t>Ringhack (savhack), färska, glest utspridda längs flera meter på en gran vid kant mot hygge. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3766,7 +3767,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
         <v>131651180</v>
       </c>
       <c r="B26" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>131651201</v>
       </c>
       <c r="B27" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>131651165</v>
       </c>
       <c r="B28" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>131651224</v>
       </c>
       <c r="B29" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>131651226</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>131651192</v>
       </c>
       <c r="B31" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131651184</v>
+        <v>131651179</v>
       </c>
       <c r="B32" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493261</v>
+        <v>493247</v>
       </c>
       <c r="R32" t="n">
-        <v>7016936</v>
+        <v>7017116</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131651183</v>
+        <v>131651184</v>
       </c>
       <c r="B33" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493286</v>
+        <v>493261</v>
       </c>
       <c r="R33" t="n">
-        <v>7016955</v>
+        <v>7016936</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4773,11 +4773,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4830,39 +4825,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131651196</v>
+        <v>131651183</v>
       </c>
       <c r="B34" t="n">
-        <v>80379</v>
+        <v>80410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4872,10 +4867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493219</v>
+        <v>493286</v>
       </c>
       <c r="R34" t="n">
-        <v>7017124</v>
+        <v>7016955</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4912,7 +4907,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
+          <t>På en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4965,10 +4960,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131651199</v>
+        <v>131651196</v>
       </c>
       <c r="B35" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4995,7 +4990,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5003,10 +5002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493372</v>
+        <v>493219</v>
       </c>
       <c r="R35" t="n">
-        <v>7017082</v>
+        <v>7017124</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5043,7 +5042,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen sälg.</t>
+          <t>Gott om lunglavsbålar på en levande sälg och en nedfallen stam av sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5096,41 +5095,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131651179</v>
+        <v>131651199</v>
       </c>
       <c r="B36" t="n">
-        <v>80408</v>
+        <v>80381</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493247</v>
+        <v>493372</v>
       </c>
       <c r="R36" t="n">
-        <v>7017116</v>
+        <v>7017082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5174,6 +5169,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en klen sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131651169</v>
+        <v>131651225</v>
       </c>
       <c r="B37" t="n">
-        <v>57912</v>
+        <v>91868</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,29 +5237,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493230</v>
+        <v>493294</v>
       </c>
       <c r="R37" t="n">
-        <v>7017123</v>
+        <v>7017032</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5309,7 +5304,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5318,6 +5313,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5343,7 +5339,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5361,10 +5357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131651225</v>
+        <v>131651169</v>
       </c>
       <c r="B38" t="n">
-        <v>91866</v>
+        <v>57914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5372,24 +5368,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5399,10 +5400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493294</v>
+        <v>493230</v>
       </c>
       <c r="R38" t="n">
-        <v>7017032</v>
+        <v>7017123</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5439,7 +5440,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en döende gran med 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5448,7 +5449,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # En döende gran med 33 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
         <v>131651193</v>
       </c>
       <c r="B39" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>131651194</v>
       </c>
       <c r="B40" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5706,35 +5706,39 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131651223</v>
+        <v>131651187</v>
       </c>
       <c r="B41" t="n">
-        <v>91866</v>
+        <v>80410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493368</v>
+        <v>493275</v>
       </c>
       <c r="R41" t="n">
-        <v>7017102</v>
+        <v>7016819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5782,11 +5786,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I en relativt grov döende gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5804,22 +5803,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5837,10 +5836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131651187</v>
+        <v>131651190</v>
       </c>
       <c r="B42" t="n">
-        <v>80408</v>
+        <v>80285</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5848,30 +5847,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5879,10 +5874,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493275</v>
+        <v>493279</v>
       </c>
       <c r="R42" t="n">
-        <v>7016819</v>
+        <v>7016965</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5917,6 +5912,11 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5967,37 +5967,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131651190</v>
+        <v>131651223</v>
       </c>
       <c r="B43" t="n">
-        <v>80283</v>
+        <v>91868</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493279</v>
+        <v>493368</v>
       </c>
       <c r="R43" t="n">
-        <v>7016965</v>
+        <v>7017102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>I en relativt grov döende gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131651200</v>
+        <v>131651222</v>
       </c>
       <c r="B44" t="n">
-        <v>80379</v>
+        <v>91844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6109,26 +6109,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493232</v>
+        <v>493220</v>
       </c>
       <c r="R44" t="n">
-        <v>7017008</v>
+        <v>7016908</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6191,27 +6195,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6229,10 +6233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131651222</v>
+        <v>131651200</v>
       </c>
       <c r="B45" t="n">
-        <v>91842</v>
+        <v>80381</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6240,30 +6244,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493220</v>
+        <v>493232</v>
       </c>
       <c r="R45" t="n">
-        <v>7016908</v>
+        <v>7017008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende gran med 35 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # En stående döende gran med 35 cm i brösthöjdsdiameter. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131651189</v>
+        <v>131651202</v>
       </c>
       <c r="B46" t="n">
-        <v>57909</v>
+        <v>80381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6375,54 +6375,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493301</v>
+        <v>493288</v>
       </c>
       <c r="R46" t="n">
-        <v>7016941</v>
+        <v>7016954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6459,7 +6442,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
+          <t>Enstaka bålar på en klenvuxen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6468,12 +6451,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6491,10 +6495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131651173</v>
+        <v>131651228</v>
       </c>
       <c r="B47" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6502,31 +6506,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6534,10 +6533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493227</v>
+        <v>493283</v>
       </c>
       <c r="R47" t="n">
-        <v>7017003</v>
+        <v>7017147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6574,7 +6573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6583,6 +6582,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6603,12 +6603,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131651202</v>
+        <v>131651229</v>
       </c>
       <c r="B48" t="n">
-        <v>80379</v>
+        <v>79276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493288</v>
+        <v>493259</v>
       </c>
       <c r="R48" t="n">
-        <v>7016954</v>
+        <v>7017152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6702,11 +6702,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en klenvuxen sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6724,22 +6719,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6757,10 +6752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131651228</v>
+        <v>131651189</v>
       </c>
       <c r="B49" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6768,37 +6763,54 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493283</v>
+        <v>493301</v>
       </c>
       <c r="R49" t="n">
-        <v>7017147</v>
+        <v>7016941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6835,7 +6847,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>En hane med sång och lockläte kom flygandes genom skogen. I denna skog finns grövre asp och tall för bohål och gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6844,33 +6856,12 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6888,10 +6879,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131651229</v>
+        <v>131651173</v>
       </c>
       <c r="B50" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6899,26 +6890,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493259</v>
+        <v>493227</v>
       </c>
       <c r="R50" t="n">
-        <v>7017152</v>
+        <v>7017003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6964,13 +6960,17 @@
           <t>2026-03-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid kant mot hygge. Högt och mycket högt livsmiljövärde för tretåig hackspett i stor del av skogsbeståndet för fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7017,7 +7017,7 @@
         <v>131651167</v>
       </c>
       <c r="B51" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>131651185</v>
       </c>
       <c r="B52" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>131651227</v>
       </c>
       <c r="B53" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>131651186</v>
       </c>
       <c r="B54" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
